--- a/vragen.xlsx
+++ b/vragen.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C800EF-91C7-4068-84F7-0FCE5F38A40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE5396F-538A-4E95-96E8-D9260CCFB505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PN1-Caput 1 Theātrum" sheetId="7" r:id="rId1"/>
     <sheet name="PN1-Caput 2 Thermae" sheetId="8" r:id="rId2"/>
-    <sheet name="PN1-Caput 3 Tempium" sheetId="9" r:id="rId3"/>
+    <sheet name="PN1-Caput 3 Templum" sheetId="9" r:id="rId3"/>
     <sheet name="PN1-Caput 123 (All)" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>

--- a/vragen.xlsx
+++ b/vragen.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE5396F-538A-4E95-96E8-D9260CCFB505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E85FF61-033A-47B1-8BD5-4F710622F290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PN1-Caput 1 Theātrum" sheetId="7" r:id="rId1"/>
     <sheet name="PN1-Caput 2 Thermae" sheetId="8" r:id="rId2"/>
     <sheet name="PN1-Caput 3 Templum" sheetId="9" r:id="rId3"/>
     <sheet name="PN1-Caput 123 (All)" sheetId="10" r:id="rId4"/>
+    <sheet name="PN1-Caput 4 Lūdus" sheetId="11" r:id="rId5"/>
+    <sheet name="PN1-Caput 5 Domus" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="1483">
   <si>
     <t>de wijn</t>
   </si>
@@ -2733,6 +2735,1761 @@
   </si>
   <si>
     <t>volgnr</t>
+  </si>
+  <si>
+    <t>lēgātus</t>
+  </si>
+  <si>
+    <t>lēgātī</t>
+  </si>
+  <si>
+    <t>de gezant; de onderbevelhebber De Galliërs stuurden gezanten naar Rome om over vrede te onderhandelen.</t>
+  </si>
+  <si>
+    <t>lūdus</t>
+  </si>
+  <si>
+    <t>lūdī</t>
+  </si>
+  <si>
+    <t>het spel; de school</t>
+  </si>
+  <si>
+    <t>populus</t>
+  </si>
+  <si>
+    <t>populī</t>
+  </si>
+  <si>
+    <t>het volk</t>
+  </si>
+  <si>
+    <t>Ndl. populair</t>
+  </si>
+  <si>
+    <t>imperātor</t>
+  </si>
+  <si>
+    <t>imperātōr-is, m.</t>
+  </si>
+  <si>
+    <t>de opperbevelhebber</t>
+  </si>
+  <si>
+    <t>sōl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sōl-is, m. </t>
+  </si>
+  <si>
+    <t>de zon</t>
+  </si>
+  <si>
+    <t>Fr. le soleil</t>
+  </si>
+  <si>
+    <t>legiō</t>
+  </si>
+  <si>
+    <t>legiōn-is, v.</t>
+  </si>
+  <si>
+    <t>het legioen</t>
+  </si>
+  <si>
+    <t>pāx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pāc-is, v. </t>
+  </si>
+  <si>
+    <t>de vrede</t>
+  </si>
+  <si>
+    <t>Fr. la paix , Eng. the peace</t>
+  </si>
+  <si>
+    <t>iūs</t>
+  </si>
+  <si>
+    <t>iūr-is, o.</t>
+  </si>
+  <si>
+    <t>het recht</t>
+  </si>
+  <si>
+    <t>mūnus</t>
+  </si>
+  <si>
+    <t>mūner-is, o.</t>
+  </si>
+  <si>
+    <t>de taak; het geschenk</t>
+  </si>
+  <si>
+    <t>nūdus</t>
+  </si>
+  <si>
+    <t>naakt; beroofd van</t>
+  </si>
+  <si>
+    <t>excitāre</t>
+  </si>
+  <si>
+    <t>excitō</t>
+  </si>
+  <si>
+    <t>(op)wekken</t>
+  </si>
+  <si>
+    <t>imperāre</t>
+  </si>
+  <si>
+    <t>imperō</t>
+  </si>
+  <si>
+    <t>bevelen; opeisen</t>
+  </si>
+  <si>
+    <t>mandāre</t>
+  </si>
+  <si>
+    <t>mandō</t>
+  </si>
+  <si>
+    <t>toevertrouwen; opdragen</t>
+  </si>
+  <si>
+    <t>portāre</t>
+  </si>
+  <si>
+    <t>portō</t>
+  </si>
+  <si>
+    <t>dragen</t>
+  </si>
+  <si>
+    <t>Fr. porter</t>
+  </si>
+  <si>
+    <t>solēre</t>
+  </si>
+  <si>
+    <t>soleō</t>
+  </si>
+  <si>
+    <t>gewoon zijn. Ik ben gewoon ’s avonds te wandelen. Ik wandel gewoonlijk ’s avonds.</t>
+  </si>
+  <si>
+    <t>vincīre</t>
+  </si>
+  <si>
+    <t>vinciō</t>
+  </si>
+  <si>
+    <t>binden; boeien</t>
+  </si>
+  <si>
+    <t>ferē</t>
+  </si>
+  <si>
+    <t>bijna; meestal</t>
+  </si>
+  <si>
+    <t>ubi</t>
+  </si>
+  <si>
+    <t>toen; wanneer. Toen de meester rechtstond, schrokken de leerlingen. Wanneer je te laat komt, moet je je aanmelden.</t>
+  </si>
+  <si>
+    <t>puer</t>
+  </si>
+  <si>
+    <t>puerī, m.</t>
+  </si>
+  <si>
+    <t>de jongen</t>
+  </si>
+  <si>
+    <t>līberī</t>
+  </si>
+  <si>
+    <t>līberōrum, m. mv.</t>
+  </si>
+  <si>
+    <t>de kinderen</t>
+  </si>
+  <si>
+    <t>vir</t>
+  </si>
+  <si>
+    <t>virī, m.</t>
+  </si>
+  <si>
+    <t>de man</t>
+  </si>
+  <si>
+    <t>ager</t>
+  </si>
+  <si>
+    <t>agrī, m.</t>
+  </si>
+  <si>
+    <t>het veld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ndl. </t>
+  </si>
+  <si>
+    <t>liber</t>
+  </si>
+  <si>
+    <t>librī, m.</t>
+  </si>
+  <si>
+    <t>het boek</t>
+  </si>
+  <si>
+    <t>Fr. le livre</t>
+  </si>
+  <si>
+    <t>magister</t>
+  </si>
+  <si>
+    <t>magistrī, m.</t>
+  </si>
+  <si>
+    <t>līber</t>
+  </si>
+  <si>
+    <t>lībera, līberum</t>
+  </si>
+  <si>
+    <t>vri</t>
+  </si>
+  <si>
+    <t>jFr. libre</t>
+  </si>
+  <si>
+    <t>miser</t>
+  </si>
+  <si>
+    <t>misera, miserum</t>
+  </si>
+  <si>
+    <t>ongelukkig</t>
+  </si>
+  <si>
+    <t>Ndl. de miserie</t>
+  </si>
+  <si>
+    <t>aeger</t>
+  </si>
+  <si>
+    <t>aegra, aegrum</t>
+  </si>
+  <si>
+    <t>ziek</t>
+  </si>
+  <si>
+    <t>niger</t>
+  </si>
+  <si>
+    <t>nigra, nigrum</t>
+  </si>
+  <si>
+    <t>zwart</t>
+  </si>
+  <si>
+    <t>pulcher</t>
+  </si>
+  <si>
+    <t>pulchra, pulchrum</t>
+  </si>
+  <si>
+    <t>mooi</t>
+  </si>
+  <si>
+    <t>sacer</t>
+  </si>
+  <si>
+    <t>sacra, sacrum</t>
+  </si>
+  <si>
+    <t>heilig; gewijd. Deze tempel is gewijd aan Diana.</t>
+  </si>
+  <si>
+    <t>Ndl. het sacrament</t>
+  </si>
+  <si>
+    <t>noster</t>
+  </si>
+  <si>
+    <t>nostra, nostrum</t>
+  </si>
+  <si>
+    <t>ons, onze</t>
+  </si>
+  <si>
+    <t>vester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vestra, vestrum </t>
+  </si>
+  <si>
+    <t>cibus</t>
+  </si>
+  <si>
+    <t>cibī</t>
+  </si>
+  <si>
+    <t>het voedsel</t>
+  </si>
+  <si>
+    <t>glōria</t>
+  </si>
+  <si>
+    <t>glōriae</t>
+  </si>
+  <si>
+    <t>de roem. Met deze film verwerft de acteur internationale roem.</t>
+  </si>
+  <si>
+    <t>Fr. la gloire</t>
+  </si>
+  <si>
+    <t>pugna</t>
+  </si>
+  <si>
+    <t>pugnae</t>
+  </si>
+  <si>
+    <t>het gevecht</t>
+  </si>
+  <si>
+    <t>victōria</t>
+  </si>
+  <si>
+    <t>victōriae</t>
+  </si>
+  <si>
+    <t>de overwinning</t>
+  </si>
+  <si>
+    <t>Fr. la victoire , Eng. the victory</t>
+  </si>
+  <si>
+    <t>beneficium</t>
+  </si>
+  <si>
+    <t>beneficiī</t>
+  </si>
+  <si>
+    <t>de weldaad</t>
+  </si>
+  <si>
+    <t>Lat. bene +</t>
+  </si>
+  <si>
+    <t>praemium</t>
+  </si>
+  <si>
+    <t>praemiī</t>
+  </si>
+  <si>
+    <t>de beloning</t>
+  </si>
+  <si>
+    <t>Ndl. de premie</t>
+  </si>
+  <si>
+    <t>maximus</t>
+  </si>
+  <si>
+    <t>zeer groot; grootste</t>
+  </si>
+  <si>
+    <t>Lat. Ndl.</t>
+  </si>
+  <si>
+    <t>laudāre</t>
+  </si>
+  <si>
+    <t>laudō</t>
+  </si>
+  <si>
+    <t>prijzen</t>
+  </si>
+  <si>
+    <t>nūntiāre</t>
+  </si>
+  <si>
+    <t>nūntiō</t>
+  </si>
+  <si>
+    <t>melden</t>
+  </si>
+  <si>
+    <t>optāre</t>
+  </si>
+  <si>
+    <t>optō</t>
+  </si>
+  <si>
+    <t>wensen</t>
+  </si>
+  <si>
+    <t>Ndl. de optie</t>
+  </si>
+  <si>
+    <t>pārēre</t>
+  </si>
+  <si>
+    <t>pāreō</t>
+  </si>
+  <si>
+    <t>gehoorzamen</t>
+  </si>
+  <si>
+    <t>praebēre</t>
+  </si>
+  <si>
+    <t>praebeō</t>
+  </si>
+  <si>
+    <t>aanbieden</t>
+  </si>
+  <si>
+    <t>quis?</t>
+  </si>
+  <si>
+    <t>(vragend vnw.)</t>
+  </si>
+  <si>
+    <t>wie?</t>
+  </si>
+  <si>
+    <t>Fr. qui?</t>
+  </si>
+  <si>
+    <t>quid?</t>
+  </si>
+  <si>
+    <t>wat?</t>
+  </si>
+  <si>
+    <t>puella</t>
+  </si>
+  <si>
+    <t>puellae</t>
+  </si>
+  <si>
+    <t>het meisje</t>
+  </si>
+  <si>
+    <t>nōtus</t>
+  </si>
+  <si>
+    <t>bekend</t>
+  </si>
+  <si>
+    <t>vērus</t>
+  </si>
+  <si>
+    <t>waar; echt</t>
+  </si>
+  <si>
+    <t>Fr. vrai</t>
+  </si>
+  <si>
+    <t>temptāre</t>
+  </si>
+  <si>
+    <t>temptō</t>
+  </si>
+  <si>
+    <t>proberen; op de proef stellen. Het slechte weer stelt de atleten zwaar op de proef.</t>
+  </si>
+  <si>
+    <t>ārdēre</t>
+  </si>
+  <si>
+    <t>ārdeō</t>
+  </si>
+  <si>
+    <t>branden</t>
+  </si>
+  <si>
+    <t>iacēre</t>
+  </si>
+  <si>
+    <t>iaceō</t>
+  </si>
+  <si>
+    <t>liggen</t>
+  </si>
+  <si>
+    <t>placēre</t>
+  </si>
+  <si>
+    <t>placeō</t>
+  </si>
+  <si>
+    <t>bevallen; aanstaan. Een heerlijke maaltijd zou me nu wel bevallen!</t>
+  </si>
+  <si>
+    <t>citō</t>
+  </si>
+  <si>
+    <t>snel</t>
+  </si>
+  <si>
+    <t>quō?</t>
+  </si>
+  <si>
+    <t>waarheen?</t>
+  </si>
+  <si>
+    <t>ergō</t>
+  </si>
+  <si>
+    <t>dus</t>
+  </si>
+  <si>
+    <t>oculus</t>
+  </si>
+  <si>
+    <t>oculī</t>
+  </si>
+  <si>
+    <t>het oog</t>
+  </si>
+  <si>
+    <t>auxilium</t>
+  </si>
+  <si>
+    <t>auxiliī</t>
+  </si>
+  <si>
+    <t>de hulp</t>
+  </si>
+  <si>
+    <t>bracchium</t>
+  </si>
+  <si>
+    <t>bracchiī</t>
+  </si>
+  <si>
+    <t>de arm</t>
+  </si>
+  <si>
+    <t>Fr. le bras</t>
+  </si>
+  <si>
+    <t>verbum</t>
+  </si>
+  <si>
+    <t>verbī</t>
+  </si>
+  <si>
+    <t>het woord</t>
+  </si>
+  <si>
+    <t>Fr. le verbe</t>
+  </si>
+  <si>
+    <t>auris</t>
+  </si>
+  <si>
+    <t>aur-is, v.</t>
+  </si>
+  <si>
+    <t>het oor</t>
+  </si>
+  <si>
+    <t>dūrus</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>Fr. dur</t>
+  </si>
+  <si>
+    <t>maestus</t>
+  </si>
+  <si>
+    <t>treurig</t>
+  </si>
+  <si>
+    <t>vīvus</t>
+  </si>
+  <si>
+    <t>levend</t>
+  </si>
+  <si>
+    <t>ōrāre</t>
+  </si>
+  <si>
+    <t>ōrō</t>
+  </si>
+  <si>
+    <t>bidden; smeken</t>
+  </si>
+  <si>
+    <t>maerēre</t>
+  </si>
+  <si>
+    <t>maereō</t>
+  </si>
+  <si>
+    <t>treuren (om). Vader treurt om het ontslag van zijn collega.</t>
+  </si>
+  <si>
+    <t>locus</t>
+  </si>
+  <si>
+    <t>locīde</t>
+  </si>
+  <si>
+    <t>plaats; de gelegenheid</t>
+  </si>
+  <si>
+    <t>Ndl. het lokaal</t>
+  </si>
+  <si>
+    <t>rāmus</t>
+  </si>
+  <si>
+    <t>rāmī</t>
+  </si>
+  <si>
+    <t>de tak</t>
+  </si>
+  <si>
+    <t>causa</t>
+  </si>
+  <si>
+    <t>causae</t>
+  </si>
+  <si>
+    <t>de oorzaak; de reden; het proces. Het proces over die moordzaak duurde drie weken.</t>
+  </si>
+  <si>
+    <t>Fr. la cause</t>
+  </si>
+  <si>
+    <t>cēna</t>
+  </si>
+  <si>
+    <t>cēnae</t>
+  </si>
+  <si>
+    <t>het avondmaal</t>
+  </si>
+  <si>
+    <t>hōra</t>
+  </si>
+  <si>
+    <t>hōrae</t>
+  </si>
+  <si>
+    <t>het uur</t>
+  </si>
+  <si>
+    <t>Fr. l’heure; l’horloge</t>
+  </si>
+  <si>
+    <t>vīlla</t>
+  </si>
+  <si>
+    <t>vīllae</t>
+  </si>
+  <si>
+    <t>de villa; het landgoed</t>
+  </si>
+  <si>
+    <t>cōnsilium</t>
+  </si>
+  <si>
+    <t>cōnsiliī</t>
+  </si>
+  <si>
+    <t>het overleg; de raad; het plan</t>
+  </si>
+  <si>
+    <t>pretium</t>
+  </si>
+  <si>
+    <t>pretiī</t>
+  </si>
+  <si>
+    <t>de prijs</t>
+  </si>
+  <si>
+    <t>flōs</t>
+  </si>
+  <si>
+    <t>flōr-is, m.</t>
+  </si>
+  <si>
+    <t>de bloem</t>
+  </si>
+  <si>
+    <t>Fr. la fleur</t>
+  </si>
+  <si>
+    <t>arbor</t>
+  </si>
+  <si>
+    <t>arbor-is, v.</t>
+  </si>
+  <si>
+    <t>de boom</t>
+  </si>
+  <si>
+    <t>Fr. l’arbre</t>
+  </si>
+  <si>
+    <t>plēnus</t>
+  </si>
+  <si>
+    <t>vol</t>
+  </si>
+  <si>
+    <t>Fr. plein</t>
+  </si>
+  <si>
+    <t>invītāre</t>
+  </si>
+  <si>
+    <t>invītō</t>
+  </si>
+  <si>
+    <t>uitnodigen</t>
+  </si>
+  <si>
+    <t>Ndl. inviteren</t>
+  </si>
+  <si>
+    <t>haerēre</t>
+  </si>
+  <si>
+    <t>haereō</t>
+  </si>
+  <si>
+    <t>vastzitten</t>
+  </si>
+  <si>
+    <t>mēnsa</t>
+  </si>
+  <si>
+    <t>mēnsae</t>
+  </si>
+  <si>
+    <t>de tafel</t>
+  </si>
+  <si>
+    <t>nāvis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nāv-is, v. </t>
+  </si>
+  <si>
+    <t>het schip</t>
+  </si>
+  <si>
+    <t>Ndl. de navigator</t>
+  </si>
+  <si>
+    <t>cupidus</t>
+  </si>
+  <si>
+    <t>vol verlangen naar</t>
+  </si>
+  <si>
+    <t>mīrus</t>
+  </si>
+  <si>
+    <t>wonderlijk</t>
+  </si>
+  <si>
+    <t>nūllus</t>
+  </si>
+  <si>
+    <t>geen</t>
+  </si>
+  <si>
+    <t>paucī</t>
+  </si>
+  <si>
+    <t>weinig; enkele</t>
+  </si>
+  <si>
+    <t>agere</t>
+  </si>
+  <si>
+    <t>agō</t>
+  </si>
+  <si>
+    <t>(voort)drijven; doen</t>
+  </si>
+  <si>
+    <t>Ndl. de agent</t>
+  </si>
+  <si>
+    <t>bibere</t>
+  </si>
+  <si>
+    <t>bibō</t>
+  </si>
+  <si>
+    <t>drinken</t>
+  </si>
+  <si>
+    <t>cognōscere</t>
+  </si>
+  <si>
+    <t>cognōscō</t>
+  </si>
+  <si>
+    <t>leren kennen; vernemen</t>
+  </si>
+  <si>
+    <t>dēsinere</t>
+  </si>
+  <si>
+    <t>dēsinō</t>
+  </si>
+  <si>
+    <t>ophouden</t>
+  </si>
+  <si>
+    <t>dīcere</t>
+  </si>
+  <si>
+    <t>dīcō</t>
+  </si>
+  <si>
+    <t>zeggen; spreken; noemen</t>
+  </si>
+  <si>
+    <t>Ndl. de dictie, Fr. dire</t>
+  </si>
+  <si>
+    <t>emere</t>
+  </si>
+  <si>
+    <t>emō</t>
+  </si>
+  <si>
+    <t>kopen</t>
+  </si>
+  <si>
+    <t>intellegere</t>
+  </si>
+  <si>
+    <t>intellegō</t>
+  </si>
+  <si>
+    <t>begrijpen</t>
+  </si>
+  <si>
+    <t>legere</t>
+  </si>
+  <si>
+    <t>legō</t>
+  </si>
+  <si>
+    <t>lezen; kiezen; verzamelen</t>
+  </si>
+  <si>
+    <t>ostendere</t>
+  </si>
+  <si>
+    <t>ostendō</t>
+  </si>
+  <si>
+    <t>tonen</t>
+  </si>
+  <si>
+    <t>quaerere</t>
+  </si>
+  <si>
+    <t>quaerō</t>
+  </si>
+  <si>
+    <t>zoeken; vragen</t>
+  </si>
+  <si>
+    <t>Fr. la question</t>
+  </si>
+  <si>
+    <t>sūmere</t>
+  </si>
+  <si>
+    <t>sūmō</t>
+  </si>
+  <si>
+    <t>nemen</t>
+  </si>
+  <si>
+    <t>vendere</t>
+  </si>
+  <si>
+    <t>vendō</t>
+  </si>
+  <si>
+    <t>verkopen</t>
+  </si>
+  <si>
+    <t>Fr. vendre</t>
+  </si>
+  <si>
+    <t>vīvere</t>
+  </si>
+  <si>
+    <t>vīvō</t>
+  </si>
+  <si>
+    <t>leven</t>
+  </si>
+  <si>
+    <t>Lat.Fr. vivre</t>
+  </si>
+  <si>
+    <t>hospes</t>
+  </si>
+  <si>
+    <t>hospit-is, m.</t>
+  </si>
+  <si>
+    <t>de gast; de gastheer</t>
+  </si>
+  <si>
+    <t>Ndl. het hospitaal</t>
+  </si>
+  <si>
+    <t>pōns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pont-is, m. </t>
+  </si>
+  <si>
+    <t>de brug</t>
+  </si>
+  <si>
+    <t>Fr. le pont</t>
+  </si>
+  <si>
+    <t>aestās</t>
+  </si>
+  <si>
+    <t>aestāt-is, v.</t>
+  </si>
+  <si>
+    <t>de zomer</t>
+  </si>
+  <si>
+    <t>Fr. l ’été</t>
+  </si>
+  <si>
+    <t>audēre</t>
+  </si>
+  <si>
+    <t>audeō</t>
+  </si>
+  <si>
+    <t>durven</t>
+  </si>
+  <si>
+    <t>docēre</t>
+  </si>
+  <si>
+    <t>doceō</t>
+  </si>
+  <si>
+    <t>onderwijzen</t>
+  </si>
+  <si>
+    <t>Ndl. de docent</t>
+  </si>
+  <si>
+    <t>tegere</t>
+  </si>
+  <si>
+    <t>tegō</t>
+  </si>
+  <si>
+    <t>bedekken; beschermen</t>
+  </si>
+  <si>
+    <t>metuere</t>
+  </si>
+  <si>
+    <t>metuō</t>
+  </si>
+  <si>
+    <t>vrezen</t>
+  </si>
+  <si>
+    <t>cōnsīdere</t>
+  </si>
+  <si>
+    <t>cōnsīdō</t>
+  </si>
+  <si>
+    <t>gaan zitten</t>
+  </si>
+  <si>
+    <t>discere</t>
+  </si>
+  <si>
+    <t>discō</t>
+  </si>
+  <si>
+    <t>studeren</t>
+  </si>
+  <si>
+    <t>dūcere</t>
+  </si>
+  <si>
+    <t>dūcō</t>
+  </si>
+  <si>
+    <t>leiden</t>
+  </si>
+  <si>
+    <t>lūdere</t>
+  </si>
+  <si>
+    <t>lūdō</t>
+  </si>
+  <si>
+    <t>spelen; bespotten</t>
+  </si>
+  <si>
+    <t>mittere</t>
+  </si>
+  <si>
+    <t>mittō</t>
+  </si>
+  <si>
+    <t>zenden; laten gaan</t>
+  </si>
+  <si>
+    <t>pōnere</t>
+  </si>
+  <si>
+    <t>pōnō</t>
+  </si>
+  <si>
+    <t>plaatsen; neerleggen</t>
+  </si>
+  <si>
+    <t>dēpōnere</t>
+  </si>
+  <si>
+    <t>dēpōnō</t>
+  </si>
+  <si>
+    <t>neerleggen</t>
+  </si>
+  <si>
+    <t>Lat. de +</t>
+  </si>
+  <si>
+    <t>relinquere</t>
+  </si>
+  <si>
+    <t>relinquō</t>
+  </si>
+  <si>
+    <t>achterlaten; verlaten</t>
+  </si>
+  <si>
+    <t>vertere</t>
+  </si>
+  <si>
+    <t>vertō</t>
+  </si>
+  <si>
+    <t>(om)keren; veranderen in</t>
+  </si>
+  <si>
+    <t>vincere</t>
+  </si>
+  <si>
+    <t>vincō</t>
+  </si>
+  <si>
+    <t>overwinnen; overtreffen</t>
+  </si>
+  <si>
+    <t>vīsere</t>
+  </si>
+  <si>
+    <t>vīsō</t>
+  </si>
+  <si>
+    <t>bezoeken</t>
+  </si>
+  <si>
+    <t>recipere</t>
+  </si>
+  <si>
+    <t>recipiō</t>
+  </si>
+  <si>
+    <t>ontvangen</t>
+  </si>
+  <si>
+    <t>Ndl. de receptie</t>
+  </si>
+  <si>
+    <t>hīc</t>
+  </si>
+  <si>
+    <t>hier</t>
+  </si>
+  <si>
+    <t>īra</t>
+  </si>
+  <si>
+    <t>īrae</t>
+  </si>
+  <si>
+    <t>de woede</t>
+  </si>
+  <si>
+    <t>poena</t>
+  </si>
+  <si>
+    <t>poenae</t>
+  </si>
+  <si>
+    <t>de boete; de straf</t>
+  </si>
+  <si>
+    <t>Fr. punir</t>
+  </si>
+  <si>
+    <t>studium</t>
+  </si>
+  <si>
+    <t>studiī</t>
+  </si>
+  <si>
+    <t>de studie; de sympathie; de ijver</t>
+  </si>
+  <si>
+    <t>famēs</t>
+  </si>
+  <si>
+    <t>fam-is, v.</t>
+  </si>
+  <si>
+    <t>de honger</t>
+  </si>
+  <si>
+    <t>Fr. la faim</t>
+  </si>
+  <si>
+    <t>fraus</t>
+  </si>
+  <si>
+    <t>fraud-is, v.</t>
+  </si>
+  <si>
+    <t>het bedrog</t>
+  </si>
+  <si>
+    <t>Ndl. de fraude</t>
+  </si>
+  <si>
+    <t>iubēre</t>
+  </si>
+  <si>
+    <t>iubeō</t>
+  </si>
+  <si>
+    <t>bevelen</t>
+  </si>
+  <si>
+    <t>surgere</t>
+  </si>
+  <si>
+    <t>surgō</t>
+  </si>
+  <si>
+    <t>opstaan</t>
+  </si>
+  <si>
+    <t>sentīre</t>
+  </si>
+  <si>
+    <t>sentiō</t>
+  </si>
+  <si>
+    <t>voelen; merken; menen</t>
+  </si>
+  <si>
+    <t>Fr. sentir</t>
+  </si>
+  <si>
+    <t>audācia</t>
+  </si>
+  <si>
+    <t>audāciae</t>
+  </si>
+  <si>
+    <t>de moed</t>
+  </si>
+  <si>
+    <t>cōnstantia</t>
+  </si>
+  <si>
+    <t>cōnstantiae</t>
+  </si>
+  <si>
+    <t>de volharding; Om de top te bereiken heb je moed en volharding nodig.</t>
+  </si>
+  <si>
+    <t>silentium</t>
+  </si>
+  <si>
+    <t>silentiī</t>
+  </si>
+  <si>
+    <t>de stilte</t>
+  </si>
+  <si>
+    <t>Fr. le silence, Eng. the silence</t>
+  </si>
+  <si>
+    <t>hiems</t>
+  </si>
+  <si>
+    <t>hiem-is, v.</t>
+  </si>
+  <si>
+    <t>de winter</t>
+  </si>
+  <si>
+    <t>virtūs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">virtūt-is, v. </t>
+  </si>
+  <si>
+    <t>de kwaliteit; de dapperheid</t>
+  </si>
+  <si>
+    <t>angustus</t>
+  </si>
+  <si>
+    <t>smal</t>
+  </si>
+  <si>
+    <t>Ndl. eng</t>
+  </si>
+  <si>
+    <t>tūtus</t>
+  </si>
+  <si>
+    <t>veilig</t>
+  </si>
+  <si>
+    <t>cadere</t>
+  </si>
+  <si>
+    <t>cadō</t>
+  </si>
+  <si>
+    <t>vallen</t>
+  </si>
+  <si>
+    <t>currere</t>
+  </si>
+  <si>
+    <t>currō</t>
+  </si>
+  <si>
+    <t>lopen</t>
+  </si>
+  <si>
+    <t>Fr. courir</t>
+  </si>
+  <si>
+    <t>petere</t>
+  </si>
+  <si>
+    <t>petō</t>
+  </si>
+  <si>
+    <t>gaan naar; vragen</t>
+  </si>
+  <si>
+    <t>Ndl. de petitie</t>
+  </si>
+  <si>
+    <t>poscere</t>
+  </si>
+  <si>
+    <t>poscō</t>
+  </si>
+  <si>
+    <t>errāre</t>
+  </si>
+  <si>
+    <t>errō</t>
+  </si>
+  <si>
+    <t>zwerven; zich vergissen</t>
+  </si>
+  <si>
+    <t>Eng. the error</t>
+  </si>
+  <si>
+    <t>flēre</t>
+  </si>
+  <si>
+    <t>fleō</t>
+  </si>
+  <si>
+    <t>wenen (om)</t>
+  </si>
+  <si>
+    <t>canere</t>
+  </si>
+  <si>
+    <t>canō</t>
+  </si>
+  <si>
+    <t>zingen; bezingen</t>
+  </si>
+  <si>
+    <t>Ndl.Fr. chanter</t>
+  </si>
+  <si>
+    <t>fingere</t>
+  </si>
+  <si>
+    <t>fingō</t>
+  </si>
+  <si>
+    <t>vormen; verzinnen</t>
+  </si>
+  <si>
+    <t>Ndl. de fictie</t>
+  </si>
+  <si>
+    <t>fluere</t>
+  </si>
+  <si>
+    <t>fluō</t>
+  </si>
+  <si>
+    <t>vloeien</t>
+  </si>
+  <si>
+    <t>ubi?</t>
+  </si>
+  <si>
+    <t>waar?</t>
+  </si>
+  <si>
+    <t>ad + acc.</t>
+  </si>
+  <si>
+    <t>(voorzetsel)</t>
+  </si>
+  <si>
+    <t>naar; (tot) bij</t>
+  </si>
+  <si>
+    <t>ante + acc.</t>
+  </si>
+  <si>
+    <t>vóór</t>
+  </si>
+  <si>
+    <t>Eng. AM</t>
+  </si>
+  <si>
+    <t>apud + acc.</t>
+  </si>
+  <si>
+    <t>bij</t>
+  </si>
+  <si>
+    <t>inter + acc.</t>
+  </si>
+  <si>
+    <t>tussen; tijdens</t>
+  </si>
+  <si>
+    <t>per + acc.</t>
+  </si>
+  <si>
+    <t>door; gedurende</t>
+  </si>
+  <si>
+    <t>post + acc.</t>
+  </si>
+  <si>
+    <t>achter; na</t>
+  </si>
+  <si>
+    <t>Eng. PM</t>
+  </si>
+  <si>
+    <t>praeter + acc.</t>
+  </si>
+  <si>
+    <t>voorbij; behalve</t>
+  </si>
+  <si>
+    <t>cum + abl.</t>
+  </si>
+  <si>
+    <t>met</t>
+  </si>
+  <si>
+    <t>dē + abl.</t>
+  </si>
+  <si>
+    <t>van; over. De kat springt van de muur. Hij vertelt een verhaal over Tantalus.</t>
+  </si>
+  <si>
+    <t>e of ex + abl.</t>
+  </si>
+  <si>
+    <t>uit; vanaf</t>
+  </si>
+  <si>
+    <t>sine + abl.</t>
+  </si>
+  <si>
+    <t>zonder</t>
+  </si>
+  <si>
+    <t>sub + abl.</t>
+  </si>
+  <si>
+    <t>onder; omstreeks</t>
+  </si>
+  <si>
+    <t>in + acc.</t>
+  </si>
+  <si>
+    <t>naar; tegen</t>
+  </si>
+  <si>
+    <t>in + abl.</t>
+  </si>
+  <si>
+    <t>in; op</t>
+  </si>
+  <si>
+    <t>saxum</t>
+  </si>
+  <si>
+    <t>saxī</t>
+  </si>
+  <si>
+    <t>het rotsblok</t>
+  </si>
+  <si>
+    <t>celeritās</t>
+  </si>
+  <si>
+    <t>celeritāt-is, v.</t>
+  </si>
+  <si>
+    <t>de snelheid</t>
+  </si>
+  <si>
+    <t>hūmānus</t>
+  </si>
+  <si>
+    <t>menselijk; beschaafd</t>
+  </si>
+  <si>
+    <t>līberāre</t>
+  </si>
+  <si>
+    <t>līberō</t>
+  </si>
+  <si>
+    <t>bevrijden</t>
+  </si>
+  <si>
+    <t>volāre</t>
+  </si>
+  <si>
+    <t>volō</t>
+  </si>
+  <si>
+    <t>vliegen</t>
+  </si>
+  <si>
+    <t>Fr. voler</t>
+  </si>
+  <si>
+    <t>caedere</t>
+  </si>
+  <si>
+    <t>caedō</t>
+  </si>
+  <si>
+    <t>hakken; doden</t>
+  </si>
+  <si>
+    <t>dēscendere</t>
+  </si>
+  <si>
+    <t>dēscendō</t>
+  </si>
+  <si>
+    <t>afdalen</t>
+  </si>
+  <si>
+    <t>Fr. Descendre</t>
+  </si>
+  <si>
+    <t>haurīre</t>
+  </si>
+  <si>
+    <t>hauriō</t>
+  </si>
+  <si>
+    <t>uitscheppen; opslokken</t>
+  </si>
+  <si>
+    <t>dēicere</t>
+  </si>
+  <si>
+    <t>dēiciō</t>
+  </si>
+  <si>
+    <t>naar beneden werpen; verdrijven</t>
+  </si>
+  <si>
+    <t>sē</t>
+  </si>
+  <si>
+    <t>zich</t>
+  </si>
+  <si>
+    <t>Fr.</t>
+  </si>
+  <si>
+    <t>ūnā</t>
+  </si>
+  <si>
+    <t>samen</t>
+  </si>
+  <si>
+    <t>cōpia</t>
+  </si>
+  <si>
+    <t>cōpiae</t>
+  </si>
+  <si>
+    <t>de hoeveelheid; de gelegenheid</t>
+  </si>
+  <si>
+    <t>sermō</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sermōn-is, m. </t>
+  </si>
+  <si>
+    <t>het gesprek; het taalgebruik</t>
+  </si>
+  <si>
+    <t>vātēs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vāt-is, m. </t>
+  </si>
+  <si>
+    <t>de waarzegger; de dichter</t>
+  </si>
+  <si>
+    <t>voluntās</t>
+  </si>
+  <si>
+    <t xml:space="preserve">voluntāt-is, v. </t>
+  </si>
+  <si>
+    <t>de wil</t>
+  </si>
+  <si>
+    <t>aureus</t>
+  </si>
+  <si>
+    <t>gouden</t>
+  </si>
+  <si>
+    <t>medius</t>
+  </si>
+  <si>
+    <t>middelste; het midden van</t>
+  </si>
+  <si>
+    <t>Ndl. de mediaan</t>
+  </si>
+  <si>
+    <t>obscūrus</t>
+  </si>
+  <si>
+    <t>duister; onbeduidend; Benidorm was vroeger een onbeduidend vissersdorp.</t>
+  </si>
+  <si>
+    <t>Fr. Obscur</t>
+  </si>
+  <si>
+    <t>brevis</t>
+  </si>
+  <si>
+    <t>~, breve; brev-is</t>
+  </si>
+  <si>
+    <t>kort</t>
+  </si>
+  <si>
+    <t>mortālis</t>
+  </si>
+  <si>
+    <t>~, mortāle; mortāl-is</t>
+  </si>
+  <si>
+    <t>sterfelijk</t>
+  </si>
+  <si>
+    <t>nōbilis</t>
+  </si>
+  <si>
+    <t>~, nōbile; nōbil-is</t>
+  </si>
+  <si>
+    <t>adellijk; beroemd</t>
+  </si>
+  <si>
+    <t>Ndl. nobel</t>
+  </si>
+  <si>
+    <t>omnis</t>
+  </si>
+  <si>
+    <t>~, omne; omn-is</t>
+  </si>
+  <si>
+    <t>geheel; elk</t>
+  </si>
+  <si>
+    <t>omnēs</t>
+  </si>
+  <si>
+    <t>~, omnia; omn-ium</t>
+  </si>
+  <si>
+    <t>alle</t>
+  </si>
+  <si>
+    <t>trīstis</t>
+  </si>
+  <si>
+    <t>~, trīste; trīst-is</t>
+  </si>
+  <si>
+    <t>droevig</t>
+  </si>
+  <si>
+    <t>audāx</t>
+  </si>
+  <si>
+    <t>~, ~; audāc-is</t>
+  </si>
+  <si>
+    <t>moedig; overmoedig</t>
+  </si>
+  <si>
+    <t>dīves</t>
+  </si>
+  <si>
+    <t>~, ~; dīvit-is</t>
+  </si>
+  <si>
+    <t>rijk</t>
+  </si>
+  <si>
+    <t>ferōx</t>
+  </si>
+  <si>
+    <t>~, ~; ferōc-is</t>
+  </si>
+  <si>
+    <t>woest; uitdagend</t>
+  </si>
+  <si>
+    <t>ingēns</t>
+  </si>
+  <si>
+    <t>~, ~; ingent-is</t>
+  </si>
+  <si>
+    <t>reusachtig</t>
+  </si>
+  <si>
+    <t>sapiēns</t>
+  </si>
+  <si>
+    <t>~, ~; sapient-is</t>
+  </si>
+  <si>
+    <t>wijs; verstandig</t>
+  </si>
+  <si>
+    <t>celer</t>
+  </si>
+  <si>
+    <t>celeris, celere; celer-is</t>
+  </si>
+  <si>
+    <t>incitāre</t>
+  </si>
+  <si>
+    <t>incitō</t>
+  </si>
+  <si>
+    <t>aanvuren</t>
+  </si>
+  <si>
+    <t>complēre</t>
+  </si>
+  <si>
+    <t>compleō</t>
+  </si>
+  <si>
+    <t>vullen</t>
+  </si>
+  <si>
+    <t>Ndl. compleet</t>
+  </si>
+  <si>
+    <t>adhūc</t>
+  </si>
+  <si>
+    <t>tot nu toe; nog altijd</t>
+  </si>
+  <si>
+    <t>diū</t>
+  </si>
+  <si>
+    <t>lange tijd</t>
   </si>
 </sst>
 </file>
@@ -13545,4 +15302,3311 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FAF778-32FE-449B-86A0-27DE52924615}">
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B2" t="s">
+        <v>899</v>
+      </c>
+      <c r="C2" t="s">
+        <v>900</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>901</v>
+      </c>
+      <c r="B3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>904</v>
+      </c>
+      <c r="B4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C4" t="s">
+        <v>906</v>
+      </c>
+      <c r="D4" t="s">
+        <v>907</v>
+      </c>
+      <c r="E4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B5" t="s">
+        <v>909</v>
+      </c>
+      <c r="C5" t="s">
+        <v>910</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>911</v>
+      </c>
+      <c r="B6" t="s">
+        <v>912</v>
+      </c>
+      <c r="C6" t="s">
+        <v>913</v>
+      </c>
+      <c r="D6" t="s">
+        <v>914</v>
+      </c>
+      <c r="E6">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>915</v>
+      </c>
+      <c r="B7" t="s">
+        <v>916</v>
+      </c>
+      <c r="C7" t="s">
+        <v>917</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>918</v>
+      </c>
+      <c r="B8" t="s">
+        <v>919</v>
+      </c>
+      <c r="C8" t="s">
+        <v>920</v>
+      </c>
+      <c r="D8" t="s">
+        <v>921</v>
+      </c>
+      <c r="E8">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>922</v>
+      </c>
+      <c r="B9" t="s">
+        <v>923</v>
+      </c>
+      <c r="C9" t="s">
+        <v>924</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>925</v>
+      </c>
+      <c r="B10" t="s">
+        <v>926</v>
+      </c>
+      <c r="C10" t="s">
+        <v>927</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>928</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>929</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>930</v>
+      </c>
+      <c r="B12" t="s">
+        <v>931</v>
+      </c>
+      <c r="C12" t="s">
+        <v>932</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>933</v>
+      </c>
+      <c r="B13" t="s">
+        <v>934</v>
+      </c>
+      <c r="C13" t="s">
+        <v>935</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>936</v>
+      </c>
+      <c r="B14" t="s">
+        <v>937</v>
+      </c>
+      <c r="C14" t="s">
+        <v>938</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>939</v>
+      </c>
+      <c r="B15" t="s">
+        <v>940</v>
+      </c>
+      <c r="C15" t="s">
+        <v>941</v>
+      </c>
+      <c r="D15" t="s">
+        <v>942</v>
+      </c>
+      <c r="E15">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>943</v>
+      </c>
+      <c r="B16" t="s">
+        <v>944</v>
+      </c>
+      <c r="C16" t="s">
+        <v>945</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>946</v>
+      </c>
+      <c r="B17" t="s">
+        <v>947</v>
+      </c>
+      <c r="C17" t="s">
+        <v>948</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>949</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>950</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>951</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>952</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>953</v>
+      </c>
+      <c r="B20" t="s">
+        <v>954</v>
+      </c>
+      <c r="C20" t="s">
+        <v>955</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>956</v>
+      </c>
+      <c r="B21" t="s">
+        <v>957</v>
+      </c>
+      <c r="C21" t="s">
+        <v>958</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>959</v>
+      </c>
+      <c r="B22" t="s">
+        <v>960</v>
+      </c>
+      <c r="C22" t="s">
+        <v>961</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>962</v>
+      </c>
+      <c r="B23" t="s">
+        <v>963</v>
+      </c>
+      <c r="C23" t="s">
+        <v>964</v>
+      </c>
+      <c r="D23" t="s">
+        <v>965</v>
+      </c>
+      <c r="E23">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>966</v>
+      </c>
+      <c r="B24" t="s">
+        <v>967</v>
+      </c>
+      <c r="C24" t="s">
+        <v>968</v>
+      </c>
+      <c r="D24" t="s">
+        <v>969</v>
+      </c>
+      <c r="E24">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>970</v>
+      </c>
+      <c r="B25" t="s">
+        <v>971</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>972</v>
+      </c>
+      <c r="B26" t="s">
+        <v>973</v>
+      </c>
+      <c r="C26" t="s">
+        <v>974</v>
+      </c>
+      <c r="D26" t="s">
+        <v>975</v>
+      </c>
+      <c r="E26">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>976</v>
+      </c>
+      <c r="B27" t="s">
+        <v>977</v>
+      </c>
+      <c r="C27" t="s">
+        <v>978</v>
+      </c>
+      <c r="D27" t="s">
+        <v>979</v>
+      </c>
+      <c r="E27">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>980</v>
+      </c>
+      <c r="B28" t="s">
+        <v>981</v>
+      </c>
+      <c r="C28" t="s">
+        <v>982</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>983</v>
+      </c>
+      <c r="B29" t="s">
+        <v>984</v>
+      </c>
+      <c r="C29" t="s">
+        <v>985</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>986</v>
+      </c>
+      <c r="B30" t="s">
+        <v>987</v>
+      </c>
+      <c r="C30" t="s">
+        <v>988</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>989</v>
+      </c>
+      <c r="B31" t="s">
+        <v>990</v>
+      </c>
+      <c r="C31" t="s">
+        <v>991</v>
+      </c>
+      <c r="D31" t="s">
+        <v>992</v>
+      </c>
+      <c r="E31">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>993</v>
+      </c>
+      <c r="B32" t="s">
+        <v>994</v>
+      </c>
+      <c r="C32" t="s">
+        <v>995</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>996</v>
+      </c>
+      <c r="B33" t="s">
+        <v>997</v>
+      </c>
+      <c r="C33" t="s">
+        <v>623</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>998</v>
+      </c>
+      <c r="B34" t="s">
+        <v>999</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D36" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E37">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E38">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E39">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E40">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E43">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E46">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B50" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E50">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E60">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E61">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E63">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D65" t="s">
+        <v>61</v>
+      </c>
+      <c r="E65">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D67" t="s">
+        <v>61</v>
+      </c>
+      <c r="E67">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E68">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E70">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D71" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E72">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E76">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E77">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E78">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E79">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>384</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31016A7C-2B2C-40F1-9983-D1DB67E86610}">
+  <dimension ref="A1:E113"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="30.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E8">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E12">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E17">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E19">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E20">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E21">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E22">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E23">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D28" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D30" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E34">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E39">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E42">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E44">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E45">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D46" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E48">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E51">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B54" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E54">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B55" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E57">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E58">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C59" t="s">
+        <v>520</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E60">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E62">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E63">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D64" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D66" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E67">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D68" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D69" t="s">
+        <v>61</v>
+      </c>
+      <c r="E69">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E71">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D72" t="s">
+        <v>61</v>
+      </c>
+      <c r="E72">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E75">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D76" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D77" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D78" t="s">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+      <c r="E79">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D81" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D82" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D83" t="s">
+        <v>61</v>
+      </c>
+      <c r="E83">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E84">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E86">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D87" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E88">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B89" t="s">
+        <v>611</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E89">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D91" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D92" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D93" t="s">
+        <v>5</v>
+      </c>
+      <c r="E93">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D94" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B95" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D95" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E96">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E97">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D98" t="s">
+        <v>5</v>
+      </c>
+      <c r="E98">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D99" t="s">
+        <v>61</v>
+      </c>
+      <c r="E99">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E100">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D101" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D102" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D103" t="s">
+        <v>103</v>
+      </c>
+      <c r="E103">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D104" t="s">
+        <v>61</v>
+      </c>
+      <c r="E104">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D105" t="s">
+        <v>5</v>
+      </c>
+      <c r="E105">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D106" t="s">
+        <v>5</v>
+      </c>
+      <c r="E106">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D107" t="s">
+        <v>5</v>
+      </c>
+      <c r="E107">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D108" t="s">
+        <v>61</v>
+      </c>
+      <c r="E108">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D109" t="s">
+        <v>61</v>
+      </c>
+      <c r="E109">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D110" t="s">
+        <v>5</v>
+      </c>
+      <c r="E110">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E111">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D112" t="s">
+        <v>5</v>
+      </c>
+      <c r="E112">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D113" t="s">
+        <v>5</v>
+      </c>
+      <c r="E113">
+        <v>496</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/vragen.xlsx
+++ b/vragen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9132EC9D-7177-47AE-9C4A-81C32A413F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FC8254-3C51-411D-BD48-4E6DF60EBB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="25580" windowHeight="13660" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PN1-Caput 1 Theātrum" sheetId="7" r:id="rId1"/>
@@ -24,8 +24,8 @@
     <sheet name="PN1-Caput 123456 (All)" sheetId="15" r:id="rId9"/>
     <sheet name="PN1-Caput 7 Amphitheātrum" sheetId="16" r:id="rId10"/>
     <sheet name="PN1-Caput 8 Circus Maximus" sheetId="17" r:id="rId11"/>
-    <sheet name="PN1-Caput 78" sheetId="18" r:id="rId12"/>
-    <sheet name="PN1-Caput 12345678" sheetId="19" r:id="rId13"/>
+    <sheet name="PN1-Caput 78 (All)" sheetId="18" r:id="rId12"/>
+    <sheet name="PN1-Caput 12345678 (All)" sheetId="19" r:id="rId13"/>
     <sheet name="PN1-Caput 9 Grieks" sheetId="20" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
